--- a/Donnees/Statisiques Environnementales et de la  gouvernace/Gouvernance/Theme_Gouvernance.xlsx
+++ b/Donnees/Statisiques Environnementales et de la  gouvernace/Gouvernance/Theme_Gouvernance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statisiques Environnementales et de la  gouvernace\Gouvernance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4A543A-F6E7-428C-B164-293EF6C15120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1552AE92-90BB-45CD-95EA-733319375B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TSN1" sheetId="1" r:id="rId1"/>
